--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_valparaiso.xlsx
@@ -76,7 +76,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:46</t>
+    <t xml:space="preserve">2026-09-09 20:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_valparaiso.xlsx
@@ -76,7 +76,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:52</t>
+    <t xml:space="preserve">2026-09-18 10:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1510,7 +1510,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
@@ -1519,12 +1519,12 @@
         <v>32</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>26.86</v>
+        <v>20.24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -1533,12 +1533,12 @@
         <v>33</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>49.58</v>
+        <v>55.34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>3</v>
@@ -1547,12 +1547,12 @@
         <v>34</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>80.08</v>
+        <v>88.66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>3</v>
@@ -1561,12 +1561,12 @@
         <v>32</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>23.84</v>
+        <v>26.86</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>3</v>
@@ -1575,12 +1575,12 @@
         <v>33</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>60.84</v>
+        <v>49.58</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>3</v>
@@ -1589,12 +1589,12 @@
         <v>34</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>93.61</v>
+        <v>80.08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>3</v>
@@ -1603,12 +1603,12 @@
         <v>32</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>22.29</v>
+        <v>23.84</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>3</v>
@@ -1617,12 +1617,12 @@
         <v>33</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>58.85</v>
+        <v>60.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>3</v>
@@ -1631,7 +1631,7 @@
         <v>34</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>93.33</v>
+        <v>93.61</v>
       </c>
     </row>
     <row r="11">
@@ -1804,7 +1804,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>3</v>
@@ -1813,12 +1813,12 @@
         <v>32</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>20.24</v>
+        <v>22.29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>3</v>
@@ -1827,12 +1827,12 @@
         <v>33</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>55.34</v>
+        <v>58.85</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>3</v>
@@ -1841,12 +1841,12 @@
         <v>34</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>88.66</v>
+        <v>93.33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1855,12 +1855,12 @@
         <v>35</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>91.03</v>
+        <v>93.19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>12</v>
@@ -1869,12 +1869,12 @@
         <v>36</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>94.08</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>12</v>
@@ -1883,12 +1883,12 @@
         <v>35</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>94.14</v>
+        <v>91.03</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>12</v>
@@ -1897,12 +1897,12 @@
         <v>36</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>96.19</v>
+        <v>94.08</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>12</v>
@@ -1911,12 +1911,12 @@
         <v>35</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>93.09</v>
+        <v>94.14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>12</v>
@@ -1925,7 +1925,7 @@
         <v>36</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>94.23</v>
+        <v>96.19</v>
       </c>
     </row>
     <row r="32">
@@ -2042,7 +2042,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>12</v>
@@ -2051,12 +2051,12 @@
         <v>35</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>93.19</v>
+        <v>93.09</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>12</v>
@@ -2065,12 +2065,12 @@
         <v>36</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>93.3</v>
+        <v>94.23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>13</v>
@@ -2079,12 +2079,12 @@
         <v>37</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>84.98</v>
+        <v>84.15</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>13</v>
@@ -2093,12 +2093,12 @@
         <v>38</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>88.95</v>
+        <v>85.83</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>13</v>
@@ -2107,12 +2107,12 @@
         <v>37</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>88.98</v>
+        <v>84.98</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>13</v>
@@ -2121,12 +2121,12 @@
         <v>38</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>86.39</v>
+        <v>88.95</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>13</v>
@@ -2135,12 +2135,12 @@
         <v>37</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>86.47</v>
+        <v>88.98</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>13</v>
@@ -2149,7 +2149,7 @@
         <v>38</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>86.14</v>
+        <v>86.39</v>
       </c>
     </row>
     <row r="48">
@@ -2266,7 +2266,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>13</v>
@@ -2275,12 +2275,12 @@
         <v>37</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>84.15</v>
+        <v>86.47</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>13</v>
@@ -2289,7 +2289,7 @@
         <v>38</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>85.83</v>
+        <v>86.14</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_valparaiso.xlsx
@@ -76,7 +76,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:42</t>
+    <t xml:space="preserve">2026-09-23 16:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_valparaiso.xlsx
@@ -76,7 +76,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 16:26</t>
+    <t xml:space="preserve">2026-10-05 06:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
